--- a/output/pdf_financials_xlsx/FNC.xlsx
+++ b/output/pdf_financials_xlsx/FNC.xlsx
@@ -5925,7 +5925,7 @@
         <v>-3.656512</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>17.400527</v>
+        <v>-17.400527</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-4330040</v>
@@ -24629,7 +24629,7 @@
         </is>
       </c>
       <c r="P181" s="5" t="n">
-        <v>17.400527</v>
+        <v>-17.400527</v>
       </c>
       <c r="Q181" s="5" t="n">
         <v>-4.33004</v>
@@ -69679,7 +69679,7 @@
         </is>
       </c>
       <c r="F661" s="5" t="n">
-        <v>1.631452</v>
+        <v>-1.631452</v>
       </c>
       <c r="G661" s="5" t="n">
         <v>-0.243215</v>

--- a/output/pdf_financials_xlsx/FNC.xlsx
+++ b/output/pdf_financials_xlsx/FNC.xlsx
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.02317</v>
+        <v>0.699056</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.096301</v>
+        <v>1.016551</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.243215</v>
+        <v>1.969019</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10.076372</v>
+        <v>2.102592</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.462405</v>
+        <v>1.620999</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1.035048</v>
@@ -922,31 +922,31 @@
         <v>0.828851</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.116941</v>
+        <v>0.782856</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.110309</v>
+        <v>2.136742</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.187762</v>
+        <v>1.801123</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.656512</v>
+        <v>1.998135</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>17.400527</v>
+        <v>2.13826</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1604817</v>
+        <v>5117545</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.876918</v>
+        <v>2.075081</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.692924</v>
+        <v>2.24365</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1.10861</v>
+        <v>2.787471</v>
       </c>
     </row>
     <row r="11">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.469164</v>
+        <v>-0.206722</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.163735</v>
+        <v>-0.756515</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.043083</v>
+        <v>-1.768887</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-9.855461</v>
+        <v>-1.881681</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.240247</v>
+        <v>-1.398841</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.865048</v>
@@ -977,7 +977,7 @@
         <v>-0.728851</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.016941</v>
+        <v>-0.682856</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-2.136742</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.100988</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>2.55223</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2.142436</v>
       </c>
     </row>
     <row r="13">
@@ -1971,13 +1971,13 @@
         <v>-5047113</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>12.435562</v>
+        <v>11.334574</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.43395</v>
+        <v>-4.98618</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>7.47321</v>
+        <v>5.330774</v>
       </c>
     </row>
     <row r="28">
@@ -2081,13 +2081,13 @@
         <v>-5047113</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>12.437807</v>
+        <v>11.336819</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.430452</v>
+        <v>-4.982682</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>7.476708</v>
+        <v>5.334272</v>
       </c>
     </row>
     <row r="30">
@@ -2328,19 +2328,19 @@
         <v>0.050012</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.558641</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.956669</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>10.357784</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5462839</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.367943</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.564117</v>
@@ -2438,19 +2438,19 @@
         <v>13.026542</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>14.955116</v>
+        <v>16.513757</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>10.012501</v>
+        <v>10.96917</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>20.668289</v>
+        <v>31.026073</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>22.808265</v>
+        <v>5462861.808265</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.031845</v>
+        <v>3.399788</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>4.013824</v>
@@ -3098,19 +3098,19 @@
         <v>0.350924</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.990479</v>
+        <v>0.431838</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.445277</v>
+        <v>0.488608</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>10.634932</v>
+        <v>0.277148</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>28522118.191685</v>
+        <v>23059279.191685</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>23.908576</v>
+        <v>21.540633</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>21.210766</v>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -43630,7 +43630,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -43678,10 +43678,10 @@
         <v>2.075081</v>
       </c>
       <c r="S384" s="5" t="n">
-        <v>-2.24365</v>
+        <v>2.24365</v>
       </c>
       <c r="T384" s="5" t="n">
-        <v>-2.787471</v>
+        <v>2.787471</v>
       </c>
     </row>
     <row r="385">
@@ -43992,7 +43992,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -48320,7 +48320,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -71104,7 +71104,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E676" s="5" t="n">

--- a/output/pdf_financials_xlsx/FNC.xlsx
+++ b/output/pdf_financials_xlsx/FNC.xlsx
@@ -745,25 +745,25 @@
         <v>0.07255200000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.584309</v>
+        <v>0.626309</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.419483</v>
+        <v>0.497483</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.161871</v>
+        <v>0.245871</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.204659</v>
+        <v>0.281659</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.095196</v>
+        <v>0.179196</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.079377</v>
+        <v>0.163377</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.280788</v>
+        <v>0.357788</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0.29173</v>
@@ -775,13 +775,13 @@
         <v>1565583</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.8550720000000001</v>
+        <v>0.975072</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.651303</v>
+        <v>0.771303</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.079176</v>
+        <v>1.192176</v>
       </c>
     </row>
     <row r="8">
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.307218</v>
+        <v>1.216475</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.342386</v>
+        <v>-2.234551</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.438243</v>
+        <v>-1.176195</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.786066</v>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.909257</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.892165</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.262048</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.307218</v>
+        <v>1.216475</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.342386</v>
+        <v>-2.234551</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.438243</v>
+        <v>-1.176195</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.786066</v>
@@ -1990,13 +1990,13 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.000844</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.003598</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.307218</v>
+        <v>1.216475</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.342386</v>
+        <v>-2.233707</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.438243</v>
+        <v>-1.176195</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.786066</v>
+        <v>-1.782468</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.203917</v>
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>62.40032173280741</v>
+        <v>247.0832808621789</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-516.2308295774432</v>
+        <v>-858.9991385808119</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-718.6471928527171</v>
+        <v>-587.7096116563068</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-808.5002557591066</v>
+        <v>-806.8715455545446</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-541.919264667489</v>
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>74.74522698781315</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-39.92591800321406</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-22.27929892577336</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -5950,13 +5950,13 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.000844</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.003598</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -6610,10 +6610,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-3624</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-6300</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -6772,19 +6772,19 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.041875</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-2443200</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-1.03479</v>
       </c>
       <c r="P114" s="3" t="n">
         <v>0</v>
@@ -6814,28 +6814,28 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>3.235266</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.920884</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.085772</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.904175</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.842333</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>2.585531</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>11.185125</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.116158</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -8011,10 +8011,10 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-3624</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-6300</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -21454,7 +21454,11 @@
           <t>Purchase of Marketable Securities</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -23068,7 +23072,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24098,7 +24106,11 @@
           <t>Purchase of Equipment</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -24764,7 +24776,11 @@
           <t>Deferred Tax Expense (Recovery)</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -25048,7 +25064,11 @@
           <t>Proceeds from Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -25998,7 +26018,11 @@
           <t>Deferred Tax Expense (Recovery)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -27034,7 +27058,11 @@
           <t>Deferred Tax Recovery</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -28354,7 +28382,11 @@
           <t>Proceeds from Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -29098,7 +29130,11 @@
           <t>Deferred Tax Recovery</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -33250,7 +33286,11 @@
           <t>Proceeds from Sale of Marketable Securities (Note 5)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -33344,7 +33384,11 @@
           <t>Share Repurchase</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -35546,7 +35590,11 @@
           <t>Share Repurchase</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -36212,7 +36260,11 @@
           <t>Amortization Expense</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -37442,7 +37494,11 @@
           <t>Amortization Expense</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -38210,7 +38266,11 @@
           <t>Amortization Expense</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -38780,7 +38840,11 @@
           <t>Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -39540,7 +39604,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -40206,7 +40274,11 @@
           <t>Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E346" s="5" t="n">
         <v>-0.909257</v>
       </c>
@@ -42034,7 +42106,11 @@
           <t>Directors Fees (Note 12)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -45492,7 +45568,11 @@
           <t>Directors Fees (Note 11)</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -53016,7 +53096,11 @@
           <t>Directors Fees (Note 10)</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -55472,7 +55556,11 @@
           <t>Directors Fees (Note 9)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -59788,7 +59876,11 @@
           <t>Directors Fees (Note 10)</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -66044,7 +66136,11 @@
           <t>Directors Fees</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -69476,7 +69572,11 @@
           <t>Deferred Income Tax Recovery (Expense)</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
@@ -71862,7 +71962,11 @@
           <t>Income Taxes Recovery (Expense)</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E684" s="5" t="n">
         <v>0.909257</v>
       </c>
